--- a/Testes/reescala/Teste populacao e gerações/Teste8/3_melhor_escala.xlsx
+++ b/Testes/reescala/Teste populacao e gerações/Teste8/3_melhor_escala.xlsx
@@ -1072,8 +1072,8 @@
       <c r="P5" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="Q5" s="4" t="n">
-        <v>1</v>
+      <c r="Q5" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="R5" s="4" t="n">
         <v>1</v>
@@ -1081,14 +1081,14 @@
       <c r="S5" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="T5" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U5" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="V5" s="5" t="n">
-        <v>0</v>
+      <c r="T5" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="U5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="W5" s="5" t="n">
         <v>0</v>
@@ -1183,8 +1183,8 @@
       <c r="P6" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="Q6" s="5" t="n">
-        <v>0</v>
+      <c r="Q6" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="R6" s="4" t="n">
         <v>1</v>
@@ -1294,8 +1294,8 @@
       <c r="P7" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="Q7" s="5" t="n">
-        <v>0</v>
+      <c r="Q7" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="R7" s="4" t="n">
         <v>1</v>
@@ -1738,8 +1738,8 @@
       <c r="P11" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="Q11" s="4" t="n">
-        <v>1</v>
+      <c r="Q11" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="R11" s="4" t="n">
         <v>1</v>
@@ -1960,8 +1960,8 @@
       <c r="P13" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="Q13" s="4" t="n">
-        <v>1</v>
+      <c r="Q13" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="R13" s="4" t="n">
         <v>1</v>
@@ -2191,11 +2191,11 @@
       <c r="S15" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="T15" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="U15" s="5" t="n">
-        <v>0</v>
+      <c r="T15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U15" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="V15" s="5" t="n">
         <v>0</v>
@@ -2443,11 +2443,11 @@
       <c r="AC17" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="AD17" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE17" s="5" t="n">
-        <v>0</v>
+      <c r="AD17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE17" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="AF17" s="5" t="n">
         <v>0</v>
@@ -3118,11 +3118,11 @@
       <c r="AF23" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="AG23" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH23" s="4" t="n">
-        <v>1</v>
+      <c r="AG23" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH23" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="AI23" s="5" t="n">
         <v>0</v>
@@ -4204,11 +4204,11 @@
       <c r="X33" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="Y33" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z33" s="5" t="n">
-        <v>0</v>
+      <c r="Y33" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z33" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="AA33" s="5" t="n">
         <v>0</v>
@@ -5113,11 +5113,11 @@
       <c r="AE41" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="AF41" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AG41" s="5" t="n">
-        <v>0</v>
+      <c r="AF41" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG41" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="AH41" s="5" t="n">
         <v>0</v>
@@ -5869,11 +5869,11 @@
       <c r="X48" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="Y48" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z48" s="4" t="n">
-        <v>1</v>
+      <c r="Y48" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z48" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="AA48" s="5" t="n">
         <v>0</v>
@@ -5884,20 +5884,20 @@
       <c r="AC48" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="AD48" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE48" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF48" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG48" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AH48" s="5" t="n">
-        <v>0</v>
+      <c r="AD48" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE48" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF48" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG48" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH48" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="AI48" s="5" t="n">
         <v>0</v>
@@ -5956,8 +5956,8 @@
       <c r="P49" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="Q49" s="5" t="n">
-        <v>0</v>
+      <c r="Q49" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="R49" s="4" t="n">
         <v>1</v>
